--- a/data/raw/sales/Week 20/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 20/Audio_Array/other_channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 20\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11374B6-A4C8-4455-9E2D-E79B0827D8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCB9A2C-588D-4B54-B441-867BDF81A91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D2C - Audio Array" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="384">
   <si>
     <t>SKU</t>
   </si>
@@ -1197,7 +1197,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1249,12 +1249,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1288,7 +1282,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1348,35 +1342,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1443,18 +1413,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2097,7 +2055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:W916"/>
+  <dimension ref="A1:W909"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -2147,146 +2105,165 @@
       <c r="W1" s="4"/>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="26" t="s">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="F2" s="28">
-        <v>8642.3700000000008</v>
+      <c r="F2">
+        <v>8642</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="26" t="s">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
         <v>309</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" t="s">
         <v>311</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" t="s">
         <v>310</v>
       </c>
-      <c r="E3" s="27">
-        <v>21</v>
-      </c>
-      <c r="F3" s="28">
-        <v>33795.760000000002</v>
+      <c r="E3">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>32401</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="26" t="s">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="27">
-        <v>5</v>
-      </c>
-      <c r="F4" s="28">
-        <v>11266.95</v>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>6862</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="26" t="s">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>8134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>5963</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C7" t="s">
+        <v>371</v>
+      </c>
+      <c r="D7" t="s">
+        <v>370</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="F5" s="28">
-        <v>4066.95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="27">
-        <v>4</v>
-      </c>
-      <c r="F6" s="28">
-        <v>11925.42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>369</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>370</v>
-      </c>
-      <c r="E7" s="27">
-        <v>3</v>
-      </c>
-      <c r="F7" s="28">
-        <v>4022.88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="27">
-        <v>0</v>
-      </c>
-      <c r="F8" s="28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="F9">
+        <v>1101</v>
+      </c>
+    </row>
     <row r="10" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3187,13 +3164,6 @@
     <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -5534,7 +5504,7 @@
       <c r="B7" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="25" t="s">
         <v>350</v>
       </c>
       <c r="D7" s="15">
@@ -5557,7 +5527,7 @@
       <c r="B8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="15">
@@ -5580,7 +5550,7 @@
       <c r="B9" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="25" t="s">
         <v>122</v>
       </c>
       <c r="D9" s="15">
@@ -5603,7 +5573,7 @@
       <c r="B10" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="25" t="s">
         <v>162</v>
       </c>
       <c r="D10" s="15">
